--- a/Output/万物有灵命令列表.xlsx
+++ b/Output/万物有灵命令列表.xlsx
@@ -197,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -225,11 +225,55 @@
         <color rgb="00B4B4B4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -313,6 +357,8 @@
     <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -678,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -698,7 +744,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>共 76 条命令  |  万物有灵: 56 条  |  万象篇: 20 条  |  分类: 17 个</t>
+          <t>共 84 条命令  |  核心与万象篇命令清单（源码 4.9 / 3.2.8）</t>
         </is>
       </c>
     </row>
@@ -871,9 +917,9 @@
           <t>▸ 基础 小计: 5 条命令</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="30" t="n"/>
       <c r="E10" s="11" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -1017,9 +1063,9 @@
           <t>▸ 战斗 小计: 5 条命令</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
+      <c r="B16" s="29" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="30" t="n"/>
       <c r="E16" s="11" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1244,9 +1290,9 @@
           <t>▸ 管理 小计: 8 条命令</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="30" t="n"/>
       <c r="E25" s="11" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -1363,9 +1409,9 @@
           <t>▸ 商店 小计: 4 条命令</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
+      <c r="B30" s="29" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="30" t="n"/>
       <c r="E30" s="11" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
@@ -1455,9 +1501,9 @@
           <t>▸ 世界 小计: 3 条命令</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
+      <c r="B34" s="29" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="30" t="n"/>
       <c r="E34" s="11" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
@@ -1574,9 +1620,9 @@
           <t>▸ 训练师 小计: 4 条命令</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
+      <c r="B39" s="29" t="n"/>
+      <c r="C39" s="29" t="n"/>
+      <c r="D39" s="30" t="n"/>
       <c r="E39" s="11" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
@@ -1774,9 +1820,9 @@
           <t>▸ 进阶 小计: 7 条命令</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
+      <c r="B47" s="29" t="n"/>
+      <c r="C47" s="29" t="n"/>
+      <c r="D47" s="30" t="n"/>
       <c r="E47" s="11" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
@@ -1947,9 +1993,9 @@
           <t>▸ 组队 小计: 6 条命令</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
-      <c r="C54" s="11" t="n"/>
-      <c r="D54" s="11" t="n"/>
+      <c r="B54" s="29" t="n"/>
+      <c r="C54" s="29" t="n"/>
+      <c r="D54" s="30" t="n"/>
       <c r="E54" s="11" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
@@ -2039,9 +2085,9 @@
           <t>▸ 世界Boss 小计: 3 条命令</t>
         </is>
       </c>
-      <c r="B58" s="11" t="n"/>
-      <c r="C58" s="11" t="n"/>
-      <c r="D58" s="11" t="n"/>
+      <c r="B58" s="29" t="n"/>
+      <c r="C58" s="29" t="n"/>
+      <c r="D58" s="30" t="n"/>
       <c r="E58" s="11" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
@@ -2158,9 +2204,9 @@
           <t>▸ 社交 小计: 4 条命令</t>
         </is>
       </c>
-      <c r="B63" s="11" t="n"/>
-      <c r="C63" s="11" t="n"/>
-      <c r="D63" s="11" t="n"/>
+      <c r="B63" s="29" t="n"/>
+      <c r="C63" s="29" t="n"/>
+      <c r="D63" s="30" t="n"/>
       <c r="E63" s="11" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
@@ -2304,9 +2350,9 @@
           <t>▸ Mod 小计: 5 条命令</t>
         </is>
       </c>
-      <c r="B69" s="11" t="n"/>
-      <c r="C69" s="11" t="n"/>
-      <c r="D69" s="11" t="n"/>
+      <c r="B69" s="29" t="n"/>
+      <c r="C69" s="29" t="n"/>
+      <c r="D69" s="30" t="n"/>
       <c r="E69" s="11" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
@@ -2369,9 +2415,9 @@
           <t>▸ 帮助 小计: 2 条命令</t>
         </is>
       </c>
-      <c r="B72" s="11" t="n"/>
-      <c r="C72" s="11" t="n"/>
-      <c r="D72" s="11" t="n"/>
+      <c r="B72" s="29" t="n"/>
+      <c r="C72" s="29" t="n"/>
+      <c r="D72" s="30" t="n"/>
       <c r="E72" s="11" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
@@ -2515,9 +2561,9 @@
           <t>▸ 万象篇-统计 小计: 5 条命令</t>
         </is>
       </c>
-      <c r="B78" s="11" t="n"/>
-      <c r="C78" s="11" t="n"/>
-      <c r="D78" s="11" t="n"/>
+      <c r="B78" s="29" t="n"/>
+      <c r="C78" s="29" t="n"/>
+      <c r="D78" s="30" t="n"/>
       <c r="E78" s="11" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
@@ -2634,9 +2680,9 @@
           <t>▸ 万象篇-装备 小计: 4 条命令</t>
         </is>
       </c>
-      <c r="B83" s="11" t="n"/>
-      <c r="C83" s="11" t="n"/>
-      <c r="D83" s="11" t="n"/>
+      <c r="B83" s="29" t="n"/>
+      <c r="C83" s="29" t="n"/>
+      <c r="D83" s="30" t="n"/>
       <c r="E83" s="11" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
@@ -2699,9 +2745,9 @@
           <t>▸ 万象篇-技能 小计: 2 条命令</t>
         </is>
       </c>
-      <c r="B86" s="11" t="n"/>
-      <c r="C86" s="11" t="n"/>
-      <c r="D86" s="11" t="n"/>
+      <c r="B86" s="29" t="n"/>
+      <c r="C86" s="29" t="n"/>
+      <c r="D86" s="30" t="n"/>
       <c r="E86" s="11" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
@@ -2845,9 +2891,9 @@
           <t>▸ 万象篇-市场 小计: 5 条命令</t>
         </is>
       </c>
-      <c r="B92" s="11" t="n"/>
-      <c r="C92" s="11" t="n"/>
-      <c r="D92" s="11" t="n"/>
+      <c r="B92" s="29" t="n"/>
+      <c r="C92" s="29" t="n"/>
+      <c r="D92" s="30" t="n"/>
       <c r="E92" s="11" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
@@ -2964,10 +3010,226 @@
           <t>▸ 万象篇-派遣 小计: 4 条命令</t>
         </is>
       </c>
-      <c r="B97" s="11" t="n"/>
-      <c r="C97" s="11" t="n"/>
-      <c r="D97" s="11" t="n"/>
+      <c r="B97" s="29" t="n"/>
+      <c r="C97" s="29" t="n"/>
+      <c r="D97" s="30" t="n"/>
       <c r="E97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="28" t="inlineStr">
+        <is>
+          <t>训练师</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>锻炼</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>.宠物 锻炼 &lt;力量/敏捷/智力/体质&gt;</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>每日最多3次，消耗10精力和100金币</t>
+        </is>
+      </c>
+      <c r="E98" s="24" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="28" t="inlineStr">
+        <is>
+          <t>社交</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>任务接受</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>.宠物 任务 接受 &lt;任务名或ID&gt;</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>接受每日或主线任务</t>
+        </is>
+      </c>
+      <c r="E99" s="24" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="28" t="inlineStr">
+        <is>
+          <t>社交</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>任务领取</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>.宠物 任务 领取 &lt;任务名或ID&gt;</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>领取已完成任务奖励</t>
+        </is>
+      </c>
+      <c r="E100" s="24" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="28" t="inlineStr">
+        <is>
+          <t>万象篇-统计</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>竞技场挑战</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>.宠物 竞技场 挑战 &lt;QQ号&gt; [宠物编号]</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>发起10分钟有效的竞技场挑战</t>
+        </is>
+      </c>
+      <c r="E101" s="24" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="28" t="inlineStr">
+        <is>
+          <t>万象篇-统计</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>季节领取</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>.宠物 季节 领取 [宠物名]</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>领取本季限定宠物，每种每季一次</t>
+        </is>
+      </c>
+      <c r="E102" s="24" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="28" t="inlineStr">
+        <is>
+          <t>万象篇-市场</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>取消出售</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>.宠物 取消出售 &lt;编号&gt;</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>取消自己的市场挂单</t>
+        </is>
+      </c>
+      <c r="E103" s="24" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="28" t="inlineStr">
+        <is>
+          <t>万象篇-派遣</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>探险加速</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>.宠物 使用 加速卡</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>立即完成一个探险或打工任务</t>
+        </is>
+      </c>
+      <c r="E104" s="24" t="inlineStr">
+        <is>
+          <t>万物有灵/万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="28" t="inlineStr">
+        <is>
+          <t>万象篇-派遣</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>全速加速</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>.宠物 使用 全速卡</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>立即完成全部探险和打工任务</t>
+        </is>
+      </c>
+      <c r="E105" s="24" t="inlineStr">
+        <is>
+          <t>万物有灵/万象篇</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="19">

--- a/Output/万物有灵命令列表.xlsx
+++ b/Output/万物有灵命令列表.xlsx
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -744,7 +744,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>共 84 条命令  |  核心与万象篇命令清单（源码 4.9 / 3.2.8）</t>
+          <t>共 88 条命令  |  核心与万象篇命令清单（源码 4.13 / 3.2.10）</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
           <t>基础</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>列表</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>.宠物 列表</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>查看队伍</t>
         </is>
@@ -863,17 +863,17 @@
           <t>基础</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>信息</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>.宠物 信息 &lt;编号&gt;</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>宠物详情</t>
         </is>
@@ -923,7 +923,7 @@
       <c r="E10" s="11" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>战斗</t>
         </is>
@@ -950,22 +950,22 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>战斗</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>斗殴</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>.宠物 斗殴 [编号] [地区]</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>肉身搏斗野外宠物</t>
         </is>
@@ -977,7 +977,7 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>战斗</t>
         </is>
@@ -1004,22 +1004,22 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>战斗</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>喂食</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>.宠物 喂食 &lt;编号|全部&gt; &lt;食物&gt; [数量]</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>喂食恢复</t>
         </is>
@@ -1031,7 +1031,7 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>战斗</t>
         </is>
@@ -1069,7 +1069,7 @@
       <c r="E16" s="11" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>管理</t>
         </is>
@@ -1096,22 +1096,22 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>管理</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>取出</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>.宠物 取出 &lt;编号&gt;</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>取出队伍</t>
         </is>
@@ -1123,7 +1123,7 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>管理</t>
         </is>
@@ -1150,22 +1150,22 @@
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>管理</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>育种</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>.宠物 育种 &lt;编号&gt; &lt;编号&gt;</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>育种繁殖(需异性)</t>
         </is>
@@ -1177,7 +1177,7 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>管理</t>
         </is>
@@ -1204,22 +1204,22 @@
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>管理</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>进化</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>.宠物 进化 &lt;编号&gt;</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>进化升级/预览</t>
         </is>
@@ -1231,7 +1231,7 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>管理</t>
         </is>
@@ -1258,22 +1258,22 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>管理</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>出售</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>.宠物 出售 &lt;编号&gt;</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>卖给保护机构</t>
         </is>
@@ -1285,1601 +1285,1633 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>▸ 管理 小计: 8 条命令</t>
-        </is>
-      </c>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="11" t="n"/>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>出售装备</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 出售装备 &lt;装备编号&gt;</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>系统回收核心装备，获得10金币</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>销毁装备</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 销毁装备 &lt;装备编号&gt;</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>直接销毁核心装备，不返还金币</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>▸ 管理 小计: 10 条命令</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="11" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>商店</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>商店</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>.宠物 商店</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>查看商店</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>商店</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>购买</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>.宠物 购买 &lt;物品&gt; [数量]</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>购买</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>商店</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>道具</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>.宠物 道具</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>查看道具</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>查看拥有的道具</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>商店</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>使用</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>.宠物 使用 &lt;道具&gt; [编号]</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>使用道具</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>▸ 商店 小计: 4 条命令</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n"/>
-      <c r="C30" s="29" t="n"/>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="11" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="B32" s="29" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="30" t="n"/>
+      <c r="E32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>世界</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>世界</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>.宠物 世界</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>查看世界状态</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>世界</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>探索</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>.宠物 探索 &lt;地区&gt;</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>探索地区</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>世界</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>地区</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>.宠物 地区</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>查看可探索地区</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>▸ 世界 小计: 3 条命令</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n"/>
-      <c r="C34" s="29" t="n"/>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="B36" s="29" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="30" t="n"/>
+      <c r="E36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>训练师</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>训练师</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>.宠物 训练师</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>查看训练师信息</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>训练师</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>锻炼</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 锻炼 [项目]</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>锻炼提升属性(每日5次)</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 锻炼 &lt;力量/敏捷/智力/体质&gt;</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>锻炼提升属性(每日3次)</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>训练师</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>装备玩家</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>.宠物 装备玩家 [装备名]</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>装备训练师装备</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>训练师</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>学习技能</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>.宠物 学习技能 [技能名]</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>学习训练师技能书</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>▸ 训练师 小计: 4 条命令</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n"/>
-      <c r="C39" s="29" t="n"/>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="11" t="n"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="B41" s="29" t="n"/>
+      <c r="C41" s="29" t="n"/>
+      <c r="D41" s="30" t="n"/>
+      <c r="E41" s="11" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>进阶</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>装备</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>.宠物 装备</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>查看装备背包(战斗掉落)</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>进阶</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>装备(穿戴)</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>.宠物 装备 &lt;编号&gt; &lt;宠物编号&gt;</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>给宠物穿装备</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>进阶</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>图鉴</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>.宠物 图鉴</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>查看图鉴收集进度</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>进阶</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>排行</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>.宠物 排行</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>查看排行榜</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>进阶</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>副本</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>.宠物 副本 [副本名] [难度] [宠物编号]</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>挑战副本Boss</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>进阶</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>神话</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>.宠物 神话</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>查看神话宠物</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>进阶</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>守护者</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>.宠物 守护者</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>挑战守护者Boss</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>▸ 进阶 小计: 7 条命令</t>
         </is>
       </c>
-      <c r="B47" s="29" t="n"/>
-      <c r="C47" s="29" t="n"/>
-      <c r="D47" s="30" t="n"/>
-      <c r="E47" s="11" t="n"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="B49" s="29" t="n"/>
+      <c r="C49" s="29" t="n"/>
+      <c r="D49" s="30" t="n"/>
+      <c r="E49" s="11" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>组队</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>组队</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>.宠物 组队</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>查看队伍状态/招募列表</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>组队</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>组队创建</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>.宠物 组队 创建 &lt;副本名/世界Boss&gt; [难度]</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>创建队伍</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>组队</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>组队加入</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>.宠物 组队 加入 @队长</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>加入队伍</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>组队</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>组队设宠</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>.宠物 组队 设宠 &lt;编号&gt;</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>设置出战宠物</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>组队</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>组队开始</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>.宠物 组队 开始</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>开始战斗(队长)</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>组队</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>组队退出</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>.宠物 组队 退出</t>
         </is>
       </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>退出队伍</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>▸ 组队 小计: 6 条命令</t>
         </is>
       </c>
-      <c r="B54" s="29" t="n"/>
-      <c r="C54" s="29" t="n"/>
-      <c r="D54" s="30" t="n"/>
-      <c r="E54" s="11" t="n"/>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
+      <c r="B56" s="29" t="n"/>
+      <c r="C56" s="29" t="n"/>
+      <c r="D56" s="30" t="n"/>
+      <c r="E56" s="11" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>世界Boss</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>世界Boss</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>.宠物 世界Boss</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>查看Boss状态</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="19" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>世界Boss</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>世界Boss攻击</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>.宠物 世界Boss 攻击 &lt;宠物编号&gt;</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>攻击Boss</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="19" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>世界Boss</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>世界Boss排行</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>.宠物 世界Boss 排行</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>查看伤害排行</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>▸ 世界Boss 小计: 3 条命令</t>
         </is>
       </c>
-      <c r="B58" s="29" t="n"/>
-      <c r="C58" s="29" t="n"/>
-      <c r="D58" s="30" t="n"/>
-      <c r="E58" s="11" t="n"/>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="20" t="inlineStr">
+      <c r="B60" s="29" t="n"/>
+      <c r="C60" s="29" t="n"/>
+      <c r="D60" s="30" t="n"/>
+      <c r="E60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>社交</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>城镇</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>.宠物 城镇</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>进入城镇</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>社交</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>NPC</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>.宠物 NPC</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>与NPC交互</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="20" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>社交</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>任务</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>.宠物 任务</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>查看任务列表</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>社交</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>公会</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>.宠物 公会</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>公会系统</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>▸ 社交 小计: 4 条命令</t>
-        </is>
-      </c>
-      <c r="B63" s="29" t="n"/>
-      <c r="C63" s="29" t="n"/>
-      <c r="D63" s="30" t="n"/>
-      <c r="E63" s="11" t="n"/>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="21" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>社交</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>任务接受</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 任务 接受 &lt;任务名或ID&gt;</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>接受每日或主线任务</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>社交</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>任务领取</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 任务 领取 &lt;任务名或ID&gt;</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>领取已完成任务奖励</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>▸ 社交 小计: 6 条命令</t>
+        </is>
+      </c>
+      <c r="B67" s="29" t="n"/>
+      <c r="C67" s="29" t="n"/>
+      <c r="D67" s="30" t="n"/>
+      <c r="E67" s="11" t="n"/>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>Mod</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>mod</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>.宠物 mod</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>查看已安装Mod</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="21" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>Mod</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>mod详情</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>.宠物 mod &lt;名称&gt;</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>查看Mod详情</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="21" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>Mod</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>mod列表</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>.宠物 mod 列表</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>查看WebUI可用Mod</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="21" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>Mod</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>mod安装</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>.宠物 mod 安装 &lt;名称&gt;</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>从WebUI安装Mod</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="21" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>安装Mod</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>Mod</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>mod卸载</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>.宠物 mod 卸载 &lt;名称&gt;</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>卸载Mod</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>▸ Mod 小计: 5 条命令</t>
         </is>
       </c>
-      <c r="B69" s="29" t="n"/>
-      <c r="C69" s="29" t="n"/>
-      <c r="D69" s="30" t="n"/>
-      <c r="E69" s="11" t="n"/>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="22" t="inlineStr">
+      <c r="B73" s="29" t="n"/>
+      <c r="C73" s="29" t="n"/>
+      <c r="D73" s="30" t="n"/>
+      <c r="E73" s="11" t="n"/>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>帮助</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>help</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>.宠物 help</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>查看帮助</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="22" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>帮助</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>help分类</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>.宠物 help &lt;分类&gt;</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>查看分类帮助</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>万物有灵</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>▸ 帮助 小计: 2 条命令</t>
         </is>
       </c>
-      <c r="B72" s="29" t="n"/>
-      <c r="C72" s="29" t="n"/>
-      <c r="D72" s="30" t="n"/>
-      <c r="E72" s="11" t="n"/>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="23" t="inlineStr">
+      <c r="B76" s="29" t="n"/>
+      <c r="C76" s="29" t="n"/>
+      <c r="D76" s="30" t="n"/>
+      <c r="E76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>万象篇-统计</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>捕捉统计</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>.宠物 捕捉统计</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>查看捕捉统计</t>
         </is>
       </c>
-      <c r="E73" s="24" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="23" t="inlineStr">
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>万象篇-统计</t>
         </is>
       </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>竞技场</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>.宠物 竞技场</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>查看竞技场积分</t>
         </is>
       </c>
-      <c r="E74" s="24" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="23" t="inlineStr">
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>万象篇-统计</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>成就</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>.宠物 成就</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>查看已解锁成就</t>
         </is>
       </c>
-      <c r="E75" s="24" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="23" t="inlineStr">
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>万象篇-统计</t>
         </is>
       </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>成就列表</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>.宠物 成就列表</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>查看全部成就</t>
         </is>
       </c>
-      <c r="E76" s="24" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="23" t="inlineStr">
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>万象篇-统计</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>季节</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>.宠物 季节</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>查看当前季节</t>
-        </is>
-      </c>
-      <c r="E77" s="24" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>查看当前季节与限定宠物</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>▸ 万象篇-统计 小计: 5 条命令</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="n"/>
-      <c r="C78" s="29" t="n"/>
-      <c r="D78" s="30" t="n"/>
-      <c r="E78" s="11" t="n"/>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="25" t="inlineStr">
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-统计</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>竞技场挑战</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 竞技场 挑战 &lt;QQ号&gt; [宠物编号]</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>发起10分钟有效的竞技场挑战</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-统计</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>季节领取</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 季节 领取 [宠物名]</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>领取限定宠物(每季/每节日每种一次)</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>▸ 万象篇-统计 小计: 7 条命令</t>
+        </is>
+      </c>
+      <c r="B84" s="29" t="n"/>
+      <c r="C84" s="29" t="n"/>
+      <c r="D84" s="30" t="n"/>
+      <c r="E84" s="11" t="n"/>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>万象篇-装备</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>宠物装备商店</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>.宠物 宠物装备商店</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>查看宠物装备商店</t>
         </is>
       </c>
-      <c r="E79" s="24" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="25" t="inlineStr">
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>万象篇-装备</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>购买宠物装备</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>.宠物 购买宠物装备 &lt;名称&gt;</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>购买宠物装备</t>
         </is>
       </c>
-      <c r="E80" s="24" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="25" t="inlineStr">
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>万象篇-装备</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>宠物装备背包</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>.宠物 宠物装备背包</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>查看已有装备</t>
         </is>
       </c>
-      <c r="E81" s="24" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="25" t="inlineStr">
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>万象篇-装备</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>穿戴装备</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>.宠物 穿戴装备 &lt;宠物编号&gt; &lt;装备名&gt;</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>宠物穿戴装备</t>
         </is>
       </c>
-      <c r="E82" s="24" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>▸ 万象篇-装备 小计: 4 条命令</t>
-        </is>
-      </c>
-      <c r="B83" s="29" t="n"/>
-      <c r="C83" s="29" t="n"/>
-      <c r="D83" s="30" t="n"/>
-      <c r="E83" s="11" t="n"/>
-    </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="26" t="inlineStr">
-        <is>
-          <t>万象篇-技能</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>宠物技能书</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>.宠物 宠物技能书</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>查看技能书</t>
-        </is>
-      </c>
-      <c r="E84" s="24" t="inlineStr">
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-装备</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>卸下装备</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 卸下装备 &lt;宠物编号&gt; [装备类型]</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>卸下装备，返还属性并回到背包</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="26" t="inlineStr">
-        <is>
-          <t>万象篇-技能</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>宠物学习技能</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 宠物学习技能 &lt;宠物编号&gt; &lt;技能书名&gt;</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>宠物学习技能书</t>
-        </is>
-      </c>
-      <c r="E85" s="24" t="inlineStr">
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-装备</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>出售宠物装备</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 出售宠物装备 &lt;名称&gt; [数量]</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>系统回收宠物装备，按商店半价结算</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>▸ 万象篇-技能 小计: 2 条命令</t>
-        </is>
-      </c>
-      <c r="B86" s="29" t="n"/>
-      <c r="C86" s="29" t="n"/>
-      <c r="D86" s="30" t="n"/>
-      <c r="E86" s="11" t="n"/>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="27" t="inlineStr">
-        <is>
-          <t>万象篇-市场</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>市场</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>.宠物 市场</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>查看市场</t>
-        </is>
-      </c>
-      <c r="E87" s="24" t="inlineStr">
-        <is>
-          <t>万象篇</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="27" t="inlineStr">
-        <is>
-          <t>万象篇-市场</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>挂售</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 挂售 &lt;宠物编号&gt; &lt;价格&gt;</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>挂售宠物</t>
-        </is>
-      </c>
-      <c r="E88" s="24" t="inlineStr">
-        <is>
-          <t>万象篇</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="27" t="inlineStr">
-        <is>
-          <t>万象篇-市场</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>购买宠物</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>.宠物 购买宠物 &lt;编号&gt;</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>购买宠物</t>
-        </is>
-      </c>
-      <c r="E89" s="24" t="inlineStr">
-        <is>
-          <t>万象篇</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="27" t="inlineStr">
-        <is>
-          <t>万象篇-市场</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>机构</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 机构</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>查看生灵保护机构</t>
-        </is>
-      </c>
-      <c r="E90" s="24" t="inlineStr">
-        <is>
-          <t>万象篇</t>
-        </is>
-      </c>
-    </row>
     <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="27" t="inlineStr">
-        <is>
-          <t>万象篇-市场</t>
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-装备</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>领养</t>
+          <t>销毁宠物装备</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>.宠物 领养 &lt;编号&gt;</t>
+          <t>.宠物 销毁宠物装备 &lt;名称&gt; [数量]</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>从生灵保护机构领养</t>
-        </is>
-      </c>
-      <c r="E91" s="24" t="inlineStr">
+          <t>直接销毁宠物装备，不返还金币</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
@@ -2888,7 +2920,7 @@
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>▸ 万象篇-市场 小计: 5 条命令</t>
+          <t>▸ 万象篇-装备 小计: 7 条命令</t>
         </is>
       </c>
       <c r="B92" s="29" t="n"/>
@@ -2897,361 +2929,436 @@
       <c r="E92" s="11" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="28" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-技能</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>宠物技能书</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 宠物技能书</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>查看技能书</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-技能</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>宠物学习技能</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 宠物学习技能 &lt;宠物编号&gt; &lt;技能书名&gt;</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>宠物学习技能书</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>▸ 万象篇-技能 小计: 2 条命令</t>
+        </is>
+      </c>
+      <c r="B95" s="29" t="n"/>
+      <c r="C95" s="29" t="n"/>
+      <c r="D95" s="30" t="n"/>
+      <c r="E95" s="11" t="n"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-市场</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>市场</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 市场</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>查看在售宠物</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-市场</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>挂售</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 挂售 &lt;宠物编号/物品名&gt; &lt;价格&gt;</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>挂售宠物或物品</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-市场</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>购买宠物</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 购买宠物 &lt;编号&gt;</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>购买宠物</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-市场</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>机构</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 机构</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>查看生灵保护机构</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-市场</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>领养</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 领养 &lt;编号&gt;</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>从生灵保护机构领养</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-市场</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>取消出售</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 取消出售 &lt;编号&gt;</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>取消自己的市场挂单</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>万象篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>▸ 万象篇-市场 小计: 6 条命令</t>
+        </is>
+      </c>
+      <c r="B102" s="29" t="n"/>
+      <c r="C102" s="29" t="n"/>
+      <c r="D102" s="30" t="n"/>
+      <c r="E102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>万象篇-派遣</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>探险</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>.宠物 探险 &lt;宠物编号&gt; &lt;区域&gt;</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>派宠物探险</t>
         </is>
       </c>
-      <c r="E93" s="24" t="inlineStr">
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="28" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>万象篇-派遣</t>
         </is>
       </c>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>探险状态</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>.宠物 探险状态</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>查看探险状态</t>
-        </is>
-      </c>
-      <c r="E94" s="24" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>查看探险进度</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="28" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>万象篇-派遣</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>打工</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>.宠物 打工 &lt;宠物编号&gt; &lt;类型&gt;</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>派宠物打工</t>
         </is>
       </c>
-      <c r="E95" s="24" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="22" customHeight="1">
-      <c r="A96" s="28" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>万象篇-派遣</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="B106" s="7" t="inlineStr">
         <is>
           <t>打工状态</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>.宠物 打工状态</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>查看打工状态</t>
-        </is>
-      </c>
-      <c r="E96" s="24" t="inlineStr">
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>查看打工进度</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>▸ 万象篇-派遣 小计: 4 条命令</t>
-        </is>
-      </c>
-      <c r="B97" s="29" t="n"/>
-      <c r="C97" s="29" t="n"/>
-      <c r="D97" s="30" t="n"/>
-      <c r="E97" s="11" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="28" t="inlineStr">
-        <is>
-          <t>训练师</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>锻炼</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 锻炼 &lt;力量/敏捷/智力/体质&gt;</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>每日最多3次，消耗10精力和100金币</t>
-        </is>
-      </c>
-      <c r="E98" s="24" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="28" t="inlineStr">
-        <is>
-          <t>社交</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>任务接受</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 任务 接受 &lt;任务名或ID&gt;</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>接受每日或主线任务</t>
-        </is>
-      </c>
-      <c r="E99" s="24" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="28" t="inlineStr">
-        <is>
-          <t>社交</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>任务领取</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 任务 领取 &lt;任务名或ID&gt;</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>领取已完成任务奖励</t>
-        </is>
-      </c>
-      <c r="E100" s="24" t="inlineStr">
-        <is>
-          <t>万物有灵</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="28" t="inlineStr">
-        <is>
-          <t>万象篇-统计</t>
-        </is>
-      </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>竞技场挑战</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 竞技场 挑战 &lt;QQ号&gt; [宠物编号]</t>
-        </is>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>发起10分钟有效的竞技场挑战</t>
-        </is>
-      </c>
-      <c r="E101" s="24" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-派遣</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>探险加速</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 使用 加速卡</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>立即完成一个派遣任务</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="28" t="inlineStr">
-        <is>
-          <t>万象篇-统计</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>季节领取</t>
-        </is>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 季节 领取 [宠物名]</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>领取本季限定宠物，每种每季一次</t>
-        </is>
-      </c>
-      <c r="E102" s="24" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>万象篇-派遣</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>全速加速</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>.宠物 使用 全速卡</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>立即完成全部派遣任务</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>万象篇</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="28" t="inlineStr">
-        <is>
-          <t>万象篇-市场</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>取消出售</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 取消出售 &lt;编号&gt;</t>
-        </is>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>取消自己的市场挂单</t>
-        </is>
-      </c>
-      <c r="E103" s="24" t="inlineStr">
-        <is>
-          <t>万象篇</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="28" t="inlineStr">
-        <is>
-          <t>万象篇-派遣</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>探险加速</t>
-        </is>
-      </c>
-      <c r="C104" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 使用 加速卡</t>
-        </is>
-      </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>立即完成一个探险或打工任务</t>
-        </is>
-      </c>
-      <c r="E104" s="24" t="inlineStr">
-        <is>
-          <t>万物有灵/万象篇</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="28" t="inlineStr">
-        <is>
-          <t>万象篇-派遣</t>
-        </is>
-      </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>全速加速</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>.宠物 使用 全速卡</t>
-        </is>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>立即完成全部探险和打工任务</t>
-        </is>
-      </c>
-      <c r="E105" s="24" t="inlineStr">
-        <is>
-          <t>万物有灵/万象篇</t>
-        </is>
-      </c>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>▸ 万象篇-派遣 小计: 6 条命令</t>
+        </is>
+      </c>
+      <c r="B109" s="29" t="n"/>
+      <c r="C109" s="29" t="n"/>
+      <c r="D109" s="30" t="n"/>
+      <c r="E109" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A72:D72"/>
+  <mergeCells count="18">
+    <mergeCell ref="A109:D109"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A67:D67"/>
     <mergeCell ref="A92:D92"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A86:D86"/>
-    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
